--- a/artfynd/A 35605-2025 artfynd.xlsx
+++ b/artfynd/A 35605-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112765156</v>
+        <v>112765163</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550042</v>
+        <v>550138</v>
       </c>
       <c r="R2" t="n">
-        <v>6894259</v>
+        <v>6894186</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112765164</v>
+        <v>112765160</v>
       </c>
       <c r="B3" t="n">
-        <v>97128</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550128</v>
+        <v>550114</v>
       </c>
       <c r="R3" t="n">
-        <v>6894196</v>
+        <v>6894176</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112765158</v>
+        <v>112765156</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550010</v>
+        <v>550042</v>
       </c>
       <c r="R4" t="n">
-        <v>6894251</v>
+        <v>6894259</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112765166</v>
+        <v>112765158</v>
       </c>
       <c r="B5" t="n">
-        <v>97161</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550149</v>
+        <v>550010</v>
       </c>
       <c r="R5" t="n">
-        <v>6894227</v>
+        <v>6894252</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112765159</v>
+        <v>112765165</v>
       </c>
       <c r="B6" t="n">
-        <v>97161</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550025</v>
+        <v>550127</v>
       </c>
       <c r="R6" t="n">
-        <v>6894174</v>
+        <v>6894225</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112765160</v>
+        <v>112765157</v>
       </c>
       <c r="B7" t="n">
-        <v>78978</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1201,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6456</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550114</v>
+        <v>550033</v>
       </c>
       <c r="R7" t="n">
-        <v>6894176</v>
+        <v>6894256</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1261,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,37 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112765165</v>
+        <v>112765159</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550128</v>
+        <v>550025</v>
       </c>
       <c r="R8" t="n">
-        <v>6894225</v>
+        <v>6894174</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1389,37 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112765157</v>
+        <v>112765166</v>
       </c>
       <c r="B9" t="n">
-        <v>56762</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550033</v>
+        <v>550148</v>
       </c>
       <c r="R9" t="n">
-        <v>6894256</v>
+        <v>6894227</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1465,11 +1430,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-06-14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>hackmärken</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,37 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112765163</v>
+        <v>112765164</v>
       </c>
       <c r="B10" t="n">
-        <v>74165</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550138</v>
+        <v>550128</v>
       </c>
       <c r="R10" t="n">
-        <v>6894186</v>
+        <v>6894196</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>

--- a/artfynd/A 35605-2025 artfynd.xlsx
+++ b/artfynd/A 35605-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765156</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765158</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765165</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765157</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765159</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765166</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,8 +1595,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112765164</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>